--- a/artfynd/A 38847-2022 artfynd.xlsx
+++ b/artfynd/A 38847-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38847-2022 artfynd.xlsx
+++ b/artfynd/A 38847-2022 artfynd.xlsx
@@ -2469,7 +2469,7 @@
         <v>113629935</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 38847-2022 artfynd.xlsx
+++ b/artfynd/A 38847-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109477806</v>
+        <v>112243230</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Berg-Andersberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523050.2097359966</v>
+        <v>523006</v>
       </c>
       <c r="R2" t="n">
-        <v>6739720.475537993</v>
+        <v>6739484</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,77 +765,82 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Uno Skog, Anton Björk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109479588</v>
+        <v>112243622</v>
       </c>
       <c r="B3" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>2062</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Berg-Andersberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523022.5511074085</v>
+        <v>523006</v>
       </c>
       <c r="R3" t="n">
-        <v>6739459.067981822</v>
+        <v>6739484</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,27 +864,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gnag av bronshjon en bit upp på samma gran.</t>
+          <t>På ytmurken granlåga med delvis avfallande bark och insektsgnag i veden från tiden då granen stod upp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,34 +893,43 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Uno Skog, Anton Björk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109477493</v>
+        <v>109477674</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,35 +937,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Berg-Andersberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523001.4707132098</v>
+        <v>523024</v>
       </c>
       <c r="R4" t="n">
-        <v>6739694.771806622</v>
+        <v>6739712</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -992,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1017,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar från förra året. Mycelmattan ljus men svagare synlig - möjligen skarp dropptaggsvamp?</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,6 +1031,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1029,15 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109478348</v>
+        <v>109477388</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,24 +1061,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523091.420287828</v>
+        <v>522967</v>
       </c>
       <c r="R5" t="n">
-        <v>6739775.914704699</v>
+        <v>6739678</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,54 +1162,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109478004</v>
+        <v>112316036</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Berg-Andersberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523085.8675136197</v>
+        <v>523040</v>
       </c>
       <c r="R6" t="n">
-        <v>6739727.05311896</v>
+        <v>6739555</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,27 +1227,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt på tallstammen.</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,68 +1247,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109477585</v>
+        <v>113629943</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Berg-Andersberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523008.2636617134</v>
+        <v>522995</v>
       </c>
       <c r="R7" t="n">
-        <v>6739703.116027299</v>
+        <v>6739550</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,27 +1324,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt på träden längs denna sida av berget, på träden i sluttningen. Även gott om skägglavar.</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,38 +1348,32 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109477528</v>
+        <v>109477427</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1422,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522997.5836274119</v>
+        <v>522967</v>
       </c>
       <c r="R8" t="n">
-        <v>6739690.840669113</v>
+        <v>6739679</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1457,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1447,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På flera granar I sluttningen.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,55 +1479,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109492840</v>
+        <v>109477493</v>
       </c>
       <c r="B9" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Berg-Andersberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523022.5511074085</v>
+        <v>523001</v>
       </c>
       <c r="R9" t="n">
-        <v>6739459.067981822</v>
+        <v>6739695</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1574,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,12 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gnag av bronshjon på samma gran där även gnag av vågbandad barkbock fanns.</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,7 +1569,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1617,61 +1587,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109477674</v>
+        <v>109477528</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Berg-Andersberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523024.3449201616</v>
+        <v>522998</v>
       </c>
       <c r="R10" t="n">
-        <v>6739712.008339508</v>
+        <v>6739691</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1703,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1713,12 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar från förra året. Mycelmattan ljus men svagare synlig - möjligen skarp dropptaggsvamp?</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,7 +1677,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1746,54 +1695,51 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112243230</v>
+        <v>109477585</v>
       </c>
       <c r="B11" t="n">
-        <v>89594</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Berg-Andersberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523006</v>
+        <v>523008</v>
       </c>
       <c r="R11" t="n">
-        <v>6739484</v>
+        <v>6739703</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1817,22 +1763,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt på träden längs denna sida av berget, på träden i sluttningen. Även gott om skägglavar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,84 +1792,69 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Uno Skog, Anton Björk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112243622</v>
+        <v>113629935</v>
       </c>
       <c r="B12" t="n">
-        <v>89934</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Berg-Andersberget, Dlr</t>
+          <t>Berg-Anndersberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523006</v>
+        <v>523031</v>
       </c>
       <c r="R12" t="n">
-        <v>6739484</v>
+        <v>6739479</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1950,7 +1886,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1960,12 +1896,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På ytmurken granlåga med delvis avfallande bark och insektsgnag i veden från tiden då granen stod upp.</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,21 +1907,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2000,61 +1916,60 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Uno Skog, Anton Björk</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112244426</v>
+        <v>109492840</v>
       </c>
       <c r="B13" t="n">
-        <v>77724</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Berg-Andersberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523094</v>
+        <v>523023</v>
       </c>
       <c r="R13" t="n">
-        <v>6739613</v>
+        <v>6739460</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2078,22 +1993,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gnag av bronshjon på samma gran där även gnag av vågbandad barkbock fanns.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2102,48 +2012,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Uno Skog, Anton Björk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112316036</v>
+        <v>109479588</v>
       </c>
       <c r="B14" t="n">
-        <v>89008</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,37 +2042,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5685</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Berg-Andersberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523040</v>
+        <v>523023</v>
       </c>
       <c r="R14" t="n">
-        <v>6739554</v>
+        <v>6739460</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2205,12 +2101,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gnag av bronshjon en bit upp på samma gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,68 +2120,65 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113629943</v>
+        <v>112244426</v>
       </c>
       <c r="B15" t="n">
-        <v>89736</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5685</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Berg-Andersberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>522995</v>
+        <v>523094</v>
       </c>
       <c r="R15" t="n">
-        <v>6739550</v>
+        <v>6739613</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,7 +2210,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2322,7 +2220,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2333,6 +2231,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2342,7 +2255,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Anton Björk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2352,12 +2265,7 @@
         <v>113629936</v>
       </c>
       <c r="B16" t="n">
-        <v>78541</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2466,15 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113629935</v>
+        <v>112244411</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,39 +2385,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Berg-Anndersberget, Dlr</t>
+          <t>Berg-Andersberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523031</v>
+        <v>523138</v>
       </c>
       <c r="R17" t="n">
-        <v>6739479</v>
+        <v>6739604</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2546,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2556,7 +2455,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2576,7 +2475,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Uno Skog, Anton Björk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2586,16 +2485,11 @@
         <v>113629934</v>
       </c>
       <c r="B18" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2701,6 +2595,671 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>112245079</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Berg-Andersberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>523162</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6739770</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På lavrik hällmark.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Uno Skog, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>109478004</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Berg-Andersberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>523086</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6739727</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt på tallstammen.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>109478348</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Berg-Andersberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>523091</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6739776</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>112244644</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Berg-Andersberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>523162</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6739770</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Uno Skog, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>109475989</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Berg-Andersberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>523106</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6739463</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>109477806</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Berg-Andersberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>523050</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6739720</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38847-2022 artfynd.xlsx
+++ b/artfynd/A 38847-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112244426</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113629936</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,6 +1045,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112243230</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1158,6 +1178,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112243622</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1282,6 +1307,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109477674</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1390,6 +1420,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112244411</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1506,6 +1541,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113629934</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1619,6 +1659,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112245079</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1731,6 +1776,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109477388</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1828,6 +1878,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112316036</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1935,6 +1990,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113629943</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2048,6 +2108,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109477427</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2156,6 +2221,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109477493</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2264,6 +2334,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109477528</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2380,6 +2455,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109477585</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2483,6 +2563,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109478004</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2591,6 +2676,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109478348</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2704,6 +2794,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112244644</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2819,6 +2914,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109475989</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2931,6 +3031,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113629935</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3044,6 +3149,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109477806</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3152,6 +3262,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109492840</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3260,8 +3375,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109479588</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>